--- a/Models/Лошади/results/Лошади - Результаты прогнозов ХВ средние.xlsx
+++ b/Models/Лошади/results/Лошади - Результаты прогнозов ХВ средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93.92</v>
+        <v>86.94</v>
       </c>
       <c r="C2" t="n">
-        <v>76.8</v>
+        <v>76.92</v>
       </c>
       <c r="D2" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>213.23</v>
+        <v>279.5</v>
       </c>
       <c r="C3" t="n">
-        <v>177.46</v>
+        <v>225.85</v>
       </c>
       <c r="D3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>180.47</v>
+        <v>209.25</v>
       </c>
       <c r="C4" t="n">
-        <v>129.18</v>
+        <v>152.38</v>
       </c>
       <c r="D4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.63</v>
+        <v>110.69</v>
       </c>
       <c r="C5" t="n">
-        <v>57.12</v>
+        <v>92.39</v>
       </c>
       <c r="D5" t="n">
-        <v>6.41</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>393.44</v>
+        <v>349.13</v>
       </c>
       <c r="C6" t="n">
-        <v>329.91</v>
+        <v>293.32</v>
       </c>
       <c r="D6" t="n">
-        <v>23.31</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="C7" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>38.23</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125.79</v>
+        <v>62.78</v>
       </c>
       <c r="C9" t="n">
-        <v>84.06999999999999</v>
+        <v>44.93</v>
       </c>
       <c r="D9" t="n">
-        <v>54.85</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="10">
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95.91</v>
+        <v>50.52</v>
       </c>
       <c r="C10" t="n">
-        <v>75.48999999999999</v>
+        <v>42.54</v>
       </c>
       <c r="D10" t="n">
-        <v>4.5</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="11">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>115.08</v>
+        <v>111.04</v>
       </c>
       <c r="C11" t="n">
-        <v>91.53</v>
+        <v>83.11</v>
       </c>
       <c r="D11" t="n">
-        <v>7.54</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="12">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>275.11</v>
+        <v>210.08</v>
       </c>
       <c r="C12" t="n">
-        <v>248.67</v>
+        <v>185.21</v>
       </c>
       <c r="D12" t="n">
-        <v>16.27</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="13">
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85.73999999999999</v>
+        <v>31.77</v>
       </c>
       <c r="C13" t="n">
-        <v>76.77</v>
+        <v>29.25</v>
       </c>
       <c r="D13" t="n">
-        <v>17.34</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="14">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>151.88</v>
+        <v>107.53</v>
       </c>
       <c r="C14" t="n">
-        <v>134.34</v>
+        <v>103.93</v>
       </c>
       <c r="D14" t="n">
-        <v>15.18</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="15">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34.75</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>22.96</v>
+        <v>49.07</v>
       </c>
       <c r="D15" t="n">
-        <v>6.52</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="16">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>511.47</v>
+        <v>550.98</v>
       </c>
       <c r="C16" t="n">
-        <v>429.35</v>
+        <v>408.71</v>
       </c>
       <c r="D16" t="n">
-        <v>10.71</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="17">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>73.84</v>
+        <v>56.94</v>
       </c>
       <c r="C17" t="n">
-        <v>58.3</v>
+        <v>48.66</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="18">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>69.28</v>
+        <v>57.79</v>
       </c>
       <c r="C18" t="n">
-        <v>61.35</v>
+        <v>48.17</v>
       </c>
       <c r="D18" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="19">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>861.92</v>
+        <v>563.14</v>
       </c>
       <c r="C19" t="n">
-        <v>702.42</v>
+        <v>483.79</v>
       </c>
       <c r="D19" t="n">
-        <v>25.8</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="20">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>34.68</v>
+        <v>42.53</v>
       </c>
       <c r="C20" t="n">
-        <v>31.65</v>
+        <v>36.47</v>
       </c>
       <c r="D20" t="n">
-        <v>5.1</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="21">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>714.8200000000001</v>
+        <v>912.48</v>
       </c>
       <c r="C21" t="n">
-        <v>609.08</v>
+        <v>780.76</v>
       </c>
       <c r="D21" t="n">
-        <v>18.13</v>
+        <v>19.89</v>
       </c>
     </row>
   </sheetData>
